--- a/data/trans_dic/IP1011-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP1011-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen sindrome de down</t>
+          <t>Menores que padecen sindrome de down (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -614,7 +615,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,54 +678,54 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,03</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -792,49 +793,49 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,14</t>
+          <t>0,0; 3,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,21</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,06</t>
+          <t>0,0; 3,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,91</t>
+          <t>0,0; 2,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,52</t>
+          <t>0,0; 1,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,6</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -897,37 +898,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,59</t>
+          <t>0,0; 3,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,94</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -937,7 +938,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,02</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,85</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,87</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1117,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 3,09</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 3,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,45</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1227,54 +1228,54 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,31</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,57</t>
+          <t>0,0; 6,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,26</t>
+          <t>0,0; 3,63</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,23</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 1,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,97</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>0,0; 2,29</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,5</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,23</t>
+          <t>0,0; 1,06</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,46</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1447,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,56</t>
+          <t>0,0; 1,92</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,43</t>
+          <t>0,0; 2,51</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,76</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,96</t>
+          <t>0,0; 2,09</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,65</t>
+          <t>0,0; 1,57</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,38</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,07</t>
+          <t>0,0; 0,95</t>
         </is>
       </c>
     </row>
@@ -1557,37 +1558,37 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,64</t>
+          <t>0,0; 0,58</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
+          <t>0,0; 0,7</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>0,08; 0,73</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
           <t>0,0; 0,62</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>0; 0,18</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>0,08; 0,81</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,62</t>
-        </is>
-      </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,53</t>
+          <t>0,0; 0,48</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,55</t>
+          <t>0,09; 0,5</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1597,7 +1598,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,25</t>
+          <t>0,0; 0,28</t>
         </is>
       </c>
     </row>
@@ -1626,4 +1627,1611 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen sindrome de down (tasa de respuesta: 99,76%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>661</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1328</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3314</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3693</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3338</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4589</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3306</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2665</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3283</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>756</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>756</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3782</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4216</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3338</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3018</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>1908</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3026</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4121</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3577</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>0; 5068</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3199</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>1266</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>1412</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>1323</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>3236</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>2735</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>0; 3922</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>0; 4963</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>602; 5250</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>0; 4641</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>0; 3563</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>1273; 7062</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>674; 6809</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>0; 4099</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1011-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP1011-Provincia-trans_dic.xlsx
@@ -788,12 +788,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,26</t>
+          <t>0,0; 3,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,53</t>
+          <t>0,0; 3,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,18</t>
+          <t>0,0; 2,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,53</t>
+          <t>0,0; 1,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,78</t>
+          <t>0,0; 4,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,37</t>
+          <t>0,0; 3,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,75</t>
+          <t>0,0; 5,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,63</t>
+          <t>0,0; 3,31</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,29</t>
+          <t>0,0; 2,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,06</t>
+          <t>0,0; 1,31</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,92</t>
+          <t>0,0; 2,12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,51</t>
+          <t>0,0; 2,76</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1473,12 +1473,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,09</t>
+          <t>0,0; 2,41</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,57</t>
+          <t>0,19; 1,64</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,95</t>
+          <t>0,0; 0,86</t>
         </is>
       </c>
     </row>
@@ -1558,12 +1558,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,58</t>
+          <t>0,0; 0,75</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,7</t>
+          <t>0,0; 0,68</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1573,32 +1573,32 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,73</t>
+          <t>0,08; 0,74</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,62</t>
+          <t>0,0; 0,67</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,48</t>
+          <t>0,0; 0,39</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,5</t>
+          <t>0,09; 0,54</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,47</t>
+          <t>0,05; 0,48</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,28</t>
+          <t>0,0; 0,27</t>
         </is>
       </c>
     </row>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3314</t>
+          <t>0; 3580</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3693</t>
+          <t>0; 3271</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3338</t>
+          <t>0; 3335</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4589</t>
+          <t>0; 4630</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3306</t>
+          <t>0; 3042</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2665</t>
+          <t>0; 3125</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3283</t>
+          <t>0; 4217</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3782</t>
+          <t>0; 3103</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 4216</t>
+          <t>0; 3845</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 3338</t>
+          <t>0; 3495</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 3018</t>
+          <t>0; 3739</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 3026</t>
+          <t>0; 3344</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 4121</t>
+          <t>0; 4534</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 3577</t>
+          <t>0; 4109</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 5068</t>
+          <t>600; 5273</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0; 3199</t>
+          <t>0; 2882</t>
         </is>
       </c>
     </row>
@@ -3165,12 +3165,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>0; 3922</t>
+          <t>0; 5134</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>0; 4963</t>
+          <t>0; 4813</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>602; 5250</t>
+          <t>602; 5312</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0; 4641</t>
+          <t>0; 5042</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0; 3563</t>
+          <t>0; 2878</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1273; 7062</t>
+          <t>1210; 7551</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>674; 6809</t>
+          <t>661; 6939</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0; 4099</t>
+          <t>0; 3914</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1011-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP1011-Provincia-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -735,27 +735,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>0,65%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>0,63%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -788,12 +788,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,53</t>
+          <t>0,0; 3,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,07</t>
+          <t>0,0; 3,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,2</t>
+          <t>0,0; 1,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,41</t>
+          <t>0,0; 1,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 5,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,04</t>
+          <t>0,0; 2,37</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1180,22 +1180,22 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>1,35%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 7,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,31</t>
+          <t>0,0; 3,26</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,4</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,31</t>
+          <t>0,0; 1,23</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1395,24 +1395,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>0,38%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,12</t>
+          <t>0,0; 2,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,96</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,76</t>
+          <t>0,0; 1,56</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1473,12 +1473,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,64</t>
+          <t>0,19; 1,65</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,86</t>
+          <t>0,0; 1,07</t>
         </is>
       </c>
     </row>
@@ -1505,32 +1505,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,75</t>
+          <t>0,08; 0,81</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,68</t>
+          <t>0,0; 0,62</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 0,53</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,74</t>
+          <t>0,0; 0,64</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,67</t>
+          <t>0,0; 0,62</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,54</t>
+          <t>0,09; 0,55</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,48</t>
+          <t>0,05; 0,47</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,27</t>
+          <t>0,0; 0,25</t>
         </is>
       </c>
     </row>
@@ -1660,14 +1660,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1971,27 +1971,27 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>661</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>656</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -2024,12 +2024,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3580</t>
+          <t>0; 3326</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3271</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2039,12 +2039,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3335</t>
+          <t>0; 3312</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3288</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4630</t>
+          <t>0; 4025</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3042</t>
+          <t>0; 3291</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>651</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3944</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3125</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4217</t>
+          <t>0; 3290</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2575,22 +2575,22 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2628,22 +2628,22 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>756</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3103</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4237</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3845</t>
+          <t>0; 3791</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>672</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3355</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 3495</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 3739</t>
+          <t>0; 3487</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2896,22 +2896,22 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -2949,24 +2949,24 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>605</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 3344</t>
+          <t>0; 3993</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3347</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 4534</t>
+          <t>0; 2465</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 4109</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>600; 5273</t>
+          <t>601; 5328</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0; 2882</t>
+          <t>0; 3572</t>
         </is>
       </c>
     </row>
@@ -3059,24 +3059,24 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
           <t>2</t>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3112,32 +3112,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>1323</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>1266</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>1412</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>1970</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>1323</t>
-        </is>
-      </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>0; 5134</t>
+          <t>601; 5849</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>0; 4813</t>
+          <t>0; 4606</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3938</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>602; 5312</t>
+          <t>0; 4386</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0; 5042</t>
+          <t>0; 4369</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0; 2878</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1210; 7551</t>
+          <t>1266; 7711</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>661; 6939</t>
+          <t>673; 6783</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0; 3914</t>
+          <t>0; 3553</t>
         </is>
       </c>
     </row>
